--- a/HFDMiceKeyPhotometry.xlsx
+++ b/HFDMiceKeyPhotometry.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F7A263-D889-43C1-97D1-84B91EC9510A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC2B259-3EE5-4259-AA82-73F96AE71802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9165" yWindow="1710" windowWidth="12690" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,7 +75,7 @@
     <t>No</t>
   </si>
   <si>
-    <t>Mice</t>
+    <t>Name</t>
   </si>
 </sst>
 </file>

--- a/HFDMiceKeyPhotometry.xlsx
+++ b/HFDMiceKeyPhotometry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC2B259-3EE5-4259-AA82-73F96AE71802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004BDC24-D2A8-4984-9AFE-B2A4157DD4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9165" yWindow="1710" windowWidth="12690" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="19">
   <si>
     <t>Sex</t>
   </si>
@@ -76,6 +76,12 @@
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>C1M3</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -393,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -588,6 +594,23 @@
         <v>31.5</v>
       </c>
     </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12">
+        <v>42.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/HFDMiceKeyPhotometry.xlsx
+++ b/HFDMiceKeyPhotometry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004BDC24-D2A8-4984-9AFE-B2A4157DD4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192A7E1A-7B05-4A83-BB1C-C76797E62D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="18">
   <si>
     <t>Sex</t>
   </si>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>C1M3</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -605,7 +602,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E12">
         <v>42.3</v>
